--- a/results/job_matches_2026-08-06.xlsx
+++ b/results/job_matches_2026-08-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer(Python)</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e81248d8fcac15</t>
+          <t>https://www.indeed.com/viewjob?jk=644b32ef05018543</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer(Python)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3b83404ecad769</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e81248d8fcac15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Java Engineer - Kafka &amp; AWS MSK Migration - Client Site</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13319eb3c1502937</t>
+          <t>https://www.indeed.com/viewjob?jk=be3b83404ecad769</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Java Engineer - Kafka &amp; AWS MSK Migration - Client Site</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BSF</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc8f770215e2b11</t>
+          <t>https://www.indeed.com/viewjob?jk=13319eb3c1502937</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Benchmark Solutions LLC</t>
+          <t>BSF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, IAM, RDS, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a715f3ec85a8b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc8f770215e2b11</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python Backend Software Engineer III - AWS / Databricks</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Neubus, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0e3150d2a50804</t>
+          <t>https://www.indeed.com/viewjob?jk=4574c28d1f57d4a2</t>
         </is>
       </c>
     </row>
@@ -1098,25 +1098,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Python Backend Software Engineer III - AWS / Databricks</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Bally's Intralot</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4574c28d1f57d4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4a5cb09b0891fe</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bally's Intralot</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4a5cb09b0891fe</t>
+          <t>https://www.indeed.com/viewjob?jk=699af075d40be5fc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
+          <t>Senior Hybrid Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699af075d40be5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=20764606d6576c1f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Security Architect</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, NoSQL, MLOps, MLflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Hybrid Infrastructure Engineer</t>
+          <t>AI Security Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20764606d6576c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Mizuho Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,199 +1301,199 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e4572b56a2bddf9a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54dff210a66c8202</t>
+          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Data Analytics Engineer IV. 4P/796</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334b1cf49bdb8aa3</t>
+          <t>https://www.indeed.com/viewjob?jk=52cb4b188a57c118</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>MO 85- Power BI and Data engineer (806590)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Fellowship Health Resources, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787d22f3f9e7baa8</t>
+          <t>https://www.indeed.com/viewjob?jk=5000cd2f1efb32c2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947fd6ed5435b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdabe0fd11a2b20</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer - Automation Engineering</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>ITgen systems</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Andes, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fa8628188db74</t>
+          <t>https://www.indeed.com/viewjob?jk=3558a4604fdf437b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mizuho Bank</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4572b56a2bddf9a</t>
+          <t>https://www.indeed.com/viewjob?jk=978c47b533d24327</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=fafd113ac8d024d0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MO 85- Power BI and Data engineer (806590)</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fellowship Health Resources, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5000cd2f1efb32c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f947249f6b00842e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdabe0fd11a2b20</t>
+          <t>https://www.indeed.com/viewjob?jk=284f70ca41d0b336</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ITgen systems</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Andes, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3558a4604fdf437b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee98575464cd3291</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=978c47b533d24327</t>
+          <t>https://www.indeed.com/viewjob?jk=063baf5a6448568c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,59 +1721,59 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a982abad7bb05fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ea7e1f2c36a21591</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca42845051be0a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5f74b5ca1d0e4c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafd113ac8d024d0</t>
+          <t>https://www.indeed.com/viewjob?jk=665101d138f0765c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f947249f6b00842e</t>
+          <t>https://www.indeed.com/viewjob?jk=d01db6639e88fcab</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Full-Stack Platform Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=284f70ca41d0b336</t>
+          <t>https://www.indeed.com/viewjob?jk=4b64ece3d83e461e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee98575464cd3291</t>
+          <t>https://www.indeed.com/viewjob?jk=766c2d4ea3852d27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=063baf5a6448568c</t>
+          <t>https://www.indeed.com/viewjob?jk=2378c1e094af5b61</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,19 +1966,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea7e1f2c36a21591</t>
+          <t>https://www.indeed.com/viewjob?jk=8e904477144f9b0f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer (GCP, BigQuery)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1987,11 +1987,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Data Modeling, ELT, dbt</t>
+          <t>Redshift, Azure, Synapse Analytics, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,102 +2001,102 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5f74b5ca1d0e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=d730d92415b574ca</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665101d138f0765c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Flexjet, LLC.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766c2d4ea3852d27</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8864424fa1770f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Engineer, Data Management</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2378c1e094af5b61</t>
+          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mid-Level Software Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rivo Holdings</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, Fact Tables</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e904477144f9b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca27788eb548ec1b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8864424fa1770f</t>
+          <t>https://www.indeed.com/viewjob?jk=d174a62833050e13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Management</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
+          <t>https://www.indeed.com/viewjob?jk=5e873d0306e737e8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rivo Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, Fact Tables</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Database Administrator IV</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
+          <t>https://www.indeed.com/viewjob?jk=224c101cb5cb9b32</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Kafka SRE Engineer</t>
+          <t>Database Administrator IV</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Zookeeper, Kafka, Kafka Connect, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc3974c262ee65</t>
+          <t>https://www.indeed.com/viewjob?jk=4752fa061c12fdd3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Radix</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d174a62833050e13</t>
+          <t>https://www.indeed.com/viewjob?jk=436f3c432785fc82</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>Senior Cloud/Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e873d0306e737e8</t>
+          <t>https://www.indeed.com/viewjob?jk=90c967cc75affe93</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solution Architect/Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AAR Corp.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Wood Dale, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
+          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Database Administrator IV</t>
+          <t>EDS Front End Architect (Remote)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224c101cb5cb9b32</t>
+          <t>https://www.indeed.com/viewjob?jk=4355de47b9364410</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Database Administrator IV</t>
+          <t>Senior Backend Developer – Python</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4752fa061c12fdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=b6d002c780515dc4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Radix</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436f3c432785fc82</t>
+          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud/Site Reliability Engineer</t>
+          <t>Senior Integration Engineer, Business Systems</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Scala, Snowflake, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c967cc75affe93</t>
+          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Solution Architect/Data Engineer</t>
+          <t>Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AAR Corp.</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wood Dale, IL, US USA</t>
+          <t>Johnston, IA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Databricks Lakehouse, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
+          <t>https://www.indeed.com/viewjob?jk=03849a706ec32867</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Backend Developer – Python</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6d002c780515dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EDS Front End Architect (Remote)</t>
+          <t>Swift Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4355de47b9364410</t>
+          <t>https://www.indeed.com/viewjob?jk=e43c280e0db347ae</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Swift Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4a885f309c1d91</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2829af5ce395bf11</t>
+          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer, Business Systems</t>
+          <t>Senior Java Backend Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Scala, Snowflake, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
+          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Databricks</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IMG</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Johnston, IA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Databricks Lakehouse, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03849a706ec32867</t>
+          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Senior Analytics Engineer - On-Site (Texas)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Southside Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c35333a91d42cd16</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
+          <t>https://www.indeed.com/viewjob?jk=b18a3410ca26c21c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, Azure DevOps</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc08cd8d0cf8f96</t>
+          <t>https://www.indeed.com/viewjob?jk=8f01cd759e7e2639</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18a3410ca26c21c</t>
+          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full-stack Swift Developer</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>NYC EMPLOYEES RETIREMENT SYS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43c280e0db347ae</t>
+          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full-stack Swift Developer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Escalon</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4a885f309c1d91</t>
+          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Hybrid)</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,42 +3251,42 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
+          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Senior Full Stack Engineer, Client Platform</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
+          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Gen AI Solutions Engineer #122</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Trulioo</t>
+          <t>Premier Cloud</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f01cd759e7e2639</t>
+          <t>https://www.indeed.com/viewjob?jk=ead4e34bd1038d2d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Oracle Fusion Senior Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f70d46bede5c9eb5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Oracle Fusion Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NYC EMPLOYEES RETIREMENT SYS</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
+          <t>https://www.indeed.com/viewjob?jk=caa8a2e6fc3e9671</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Escalon</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,129 +3436,129 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
+          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>Eko Green Industrial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr Data Scientist- Generative AI</t>
+          <t>Full Stack Application Developer III 4P/797</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>S3, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e688727eb8dea1de</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0a2d794a3a9143</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Client Platform</t>
+          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3575,356 +3575,6 @@
         </is>
       </c>
       <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Sequoia Financial Group</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Bloomington, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a63fd992df921e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Gen AI Solutions Engineer #122</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Premier Cloud</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ead4e34bd1038d2d</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Oracle Fusion Senior Architect</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>BDO</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f70d46bede5c9eb5</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Oracle Fusion Architect</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>BDO</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=caa8a2e6fc3e9671</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>IT Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Brown University Health</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Providence, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=05587d106373823e</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Cloud Architect - Product Owner</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3875498686bde6</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>AssistRx</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Ascendion</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Eko Green Industrial</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Miami Lakes, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
         </is>

--- a/results/job_matches_2026-08-06.xlsx
+++ b/results/job_matches_2026-08-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Database Administrator (Senior)</t>
+          <t>Data Warehousing Specialist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Systems Development and Analysis</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, ECS, RDS, Databricks</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01de34b2c0542448</t>
+          <t>https://www.indeed.com/viewjob?jk=1f0db046b81c4b7e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Warehousing Specialist</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, ECS, RDS, Databricks</t>
+          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f0db046b81c4b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4680bf14d32cc9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Full Stack Java with Angular - Onsite - Atlanta/Alpharetta</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4680bf14d32cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=2c752e537cd0c2e4</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Senior Architect</t>
+          <t>Python Backend Software Engineer III - AWS / Databricks</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d8b3a17d5ca1b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4574c28d1f57d4a2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Python Backend Software Engineer III - AWS / Databricks</t>
+          <t>Cloud &amp; Data Senior Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4574c28d1f57d4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=56d8b3a17d5ca1b6</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
+          <t>DevOps Engineer (GovCloud/FedRAMP)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699af075d40be5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Hybrid Infrastructure Engineer</t>
+          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20764606d6576c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=699af075d40be5fc</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Data Analytics Engineer IV. 4P/796</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HBase, Spark, Scala, Kafka, MongoDB, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975478975181c2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=52cb4b188a57c118</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer IV. 4P/796</t>
+          <t>MO 85- Power BI and Data engineer (806590)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Fellowship Health Resources, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52cb4b188a57c118</t>
+          <t>https://www.indeed.com/viewjob?jk=5000cd2f1efb32c2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MO 85- Power BI and Data engineer (806590)</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fellowship Health Resources, Inc.</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5000cd2f1efb32c2</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdabe0fd11a2b20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>ITgen systems</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Andes, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdabe0fd11a2b20</t>
+          <t>https://www.indeed.com/viewjob?jk=3558a4604fdf437b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ITgen systems</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Andes, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3558a4604fdf437b</t>
+          <t>https://www.indeed.com/viewjob?jk=978c47b533d24327</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=978c47b533d24327</t>
+          <t>https://www.indeed.com/viewjob?jk=fafd113ac8d024d0</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafd113ac8d024d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f947249f6b00842e</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f947249f6b00842e</t>
+          <t>https://www.indeed.com/viewjob?jk=284f70ca41d0b336</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=284f70ca41d0b336</t>
+          <t>https://www.indeed.com/viewjob?jk=ee98575464cd3291</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee98575464cd3291</t>
+          <t>https://www.indeed.com/viewjob?jk=063baf5a6448568c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=063baf5a6448568c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea7e1f2c36a21591</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea7e1f2c36a21591</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5f74b5ca1d0e4c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5f74b5ca1d0e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=665101d138f0765c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665101d138f0765c</t>
+          <t>https://www.indeed.com/viewjob?jk=d01db6639e88fcab</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Full-Stack Platform Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01db6639e88fcab</t>
+          <t>https://www.indeed.com/viewjob?jk=4b64ece3d83e461e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full-Stack Platform Software Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b64ece3d83e461e</t>
+          <t>https://www.indeed.com/viewjob?jk=766c2d4ea3852d27</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766c2d4ea3852d27</t>
+          <t>https://www.indeed.com/viewjob?jk=2378c1e094af5b61</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>AI/ML ENG III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Fujitsu</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2378c1e094af5b61</t>
+          <t>https://www.indeed.com/viewjob?jk=c79fecb88f759cdc</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Management</t>
+          <t>Engineer III - Platform Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
+          <t>https://www.indeed.com/viewjob?jk=93749d43fe3ef5d1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Engineer, Data Management</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rivo Holdings</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, Fact Tables</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
+          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Rivo Holdings</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, Fact Tables</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
+          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d174a62833050e13</t>
+          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e873d0306e737e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d174a62833050e13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
+          <t>https://www.indeed.com/viewjob?jk=5e873d0306e737e8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Java Full Stack Software Engineer III - React / PostgreSQL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=5098c1122253111e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Database Administrator IV</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224c101cb5cb9b32</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Database Administrator IV</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4752fa061c12fdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Administrator IV</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Radix</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436f3c432785fc82</t>
+          <t>https://www.indeed.com/viewjob?jk=224c101cb5cb9b32</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud/Site Reliability Engineer</t>
+          <t>Database Administrator IV</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c967cc75affe93</t>
+          <t>https://www.indeed.com/viewjob?jk=4752fa061c12fdd3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Solution Architect/Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AAR Corp.</t>
+          <t>Radix</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wood Dale, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
+          <t>https://www.indeed.com/viewjob?jk=436f3c432785fc82</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud/Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=90c967cc75affe93</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EDS Front End Architect (Remote)</t>
+          <t>Solution Architect/Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>AAR Corp.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wood Dale, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4355de47b9364410</t>
+          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Backend Developer – Python</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6d002c780515dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>EDS Front End Architect (Remote)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
+          <t>https://www.indeed.com/viewjob?jk=4355de47b9364410</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer, Business Systems</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Scala, Snowflake, Oracle, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
+          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Databricks</t>
+          <t>Senior Integration Engineer, Business Systems</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IMG</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Johnston, IA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Databricks Lakehouse, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Scala, Snowflake, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03849a706ec32867</t>
+          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Senior Backend Developer – Python</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b6d002c780515dc4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Johnston, IA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Databricks Lakehouse, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
+          <t>https://www.indeed.com/viewjob?jk=03849a706ec32867</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Swift Developer</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43c280e0db347ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Swift Developer</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4a885f309c1d91</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Swift Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e43c280e0db347ae</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Hybrid)</t>
+          <t>Swift Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4a885f309c1d91</t>
         </is>
       </c>
     </row>
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
+          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - On-Site (Texas)</t>
+          <t>Senior Java Backend Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Southside Bank</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c35333a91d42cd16</t>
+          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18a3410ca26c21c</t>
+          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Analytics Engineer - On-Site (Texas)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Trulioo</t>
+          <t>Southside Bank</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f01cd759e7e2639</t>
+          <t>https://www.indeed.com/viewjob?jk=c35333a91d42cd16</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8f01cd759e7e2639</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NYC EMPLOYEES RETIREMENT SYS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
+          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Escalon</t>
+          <t>NYC EMPLOYEES RETIREMENT SYS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
+          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>Escalon</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
+          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Client Platform</t>
+          <t>Associate AI Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Gen AI Solutions Engineer #122</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Premier Cloud</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead4e34bd1038d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=b18a3410ca26c21c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Oracle Fusion Senior Architect</t>
+          <t>Senior Full Stack Engineer, Client Platform</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70d46bede5c9eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Oracle Fusion Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, Scala, ELT, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa8a2e6fc3e9671</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce11b9433c91a10</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Gen AI Solutions Engineer #122</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Premier Cloud</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
+          <t>https://www.indeed.com/viewjob?jk=ead4e34bd1038d2d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Oracle Fusion Senior Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
+          <t>https://www.indeed.com/viewjob?jk=f70d46bede5c9eb5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
+          <t>Oracle Fusion Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Eko Green Industrial</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=caa8a2e6fc3e9671</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer III 4P/797</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0a2d794a3a9143</t>
+          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Ketch</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,15 +3566,155 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ascendion</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Eko Green Industrial</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Miami Lakes, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Full Stack Application Developer III 4P/797</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>4P Consulting Inc.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb0a2d794a3a9143</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
         </is>

--- a/results/job_matches_2026-08-06.xlsx
+++ b/results/job_matches_2026-08-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Python Backend Software Engineer III - AWS / Databricks</t>
+          <t>Cloud &amp; Data Senior Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Databricks, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4574c28d1f57d4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=56d8b3a17d5ca1b6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Senior Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d8b3a17d5ca1b6</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Bally's Intralot</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4a5cb09b0891fe</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>DevOps Engineer (GovCloud/FedRAMP)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bally's Intralot</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4a5cb09b0891fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GovCloud/FedRAMP)</t>
+          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
+          <t>https://www.indeed.com/viewjob?jk=699af075d40be5fc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
+          <t>Sr Solutions Architect - Digital Customer Experience</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699af075d40be5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c2dc5b2bfc7d7bdc</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Data Modeling, ELT, dbt</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5f74b5ca1d0e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=eef1687719f12bcd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665101d138f0765c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5f74b5ca1d0e4c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01db6639e88fcab</t>
+          <t>https://www.indeed.com/viewjob?jk=665101d138f0765c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full-Stack Platform Software Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b64ece3d83e461e</t>
+          <t>https://www.indeed.com/viewjob?jk=d01db6639e88fcab</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Full-Stack Platform Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766c2d4ea3852d27</t>
+          <t>https://www.indeed.com/viewjob?jk=4b64ece3d83e461e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2378c1e094af5b61</t>
+          <t>https://www.indeed.com/viewjob?jk=766c2d4ea3852d27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI/ML ENG III</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fujitsu</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c79fecb88f759cdc</t>
+          <t>https://www.indeed.com/viewjob?jk=2378c1e094af5b61</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mid-Level Software Engineer</t>
+          <t>AI/ML ENG III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fujitsu</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e904477144f9b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=c79fecb88f759cdc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, BigQuery)</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Synapse Analytics, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d730d92415b574ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8e904477144f9b0f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Engineer (GCP, BigQuery)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>Redshift, Azure, Synapse Analytics, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d730d92415b574ca</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8864424fa1770f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer III - Platform Data Engineer (Remote)</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Flexjet, LLC.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93749d43fe3ef5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8864424fa1770f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Management</t>
+          <t>Engineer III - Platform Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
+          <t>https://www.indeed.com/viewjob?jk=93749d43fe3ef5d1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Engineer, Data Management</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rivo Holdings</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, Fact Tables</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
+          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Rivo Holdings</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, Fact Tables</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
+          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d174a62833050e13</t>
+          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>Java Full Stack Software Engineer III - React / PostgreSQL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e873d0306e737e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5098c1122253111e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java Full Stack Software Engineer III - React / PostgreSQL</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5098c1122253111e</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
+          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Database Administrator IV</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=224c101cb5cb9b32</t>
         </is>
       </c>
     </row>
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224c101cb5cb9b32</t>
+          <t>https://www.indeed.com/viewjob?jk=4752fa061c12fdd3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Database Administrator IV</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4752fa061c12fdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=5e873d0306e737e8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 3 - Virtual</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Radix</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436f3c432785fc82</t>
+          <t>https://www.indeed.com/viewjob?jk=e58245a6fd122ca7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Cloud/Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>Radix</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c967cc75affe93</t>
+          <t>https://www.indeed.com/viewjob?jk=436f3c432785fc82</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Solution Architect/Data Engineer</t>
+          <t>Senior Cloud/Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AAR Corp.</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wood Dale, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
+          <t>https://www.indeed.com/viewjob?jk=90c967cc75affe93</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect/Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>AAR Corp.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wood Dale, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EDS Front End Architect (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4355de47b9364410</t>
+          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>EDS Front End Architect (Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
+          <t>https://www.indeed.com/viewjob?jk=4355de47b9364410</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer, Business Systems</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Scala, Snowflake, Oracle, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
+          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Backend Developer – Python</t>
+          <t>Senior Integration Engineer, Business Systems</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Scala, Snowflake, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6d002c780515dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
         </is>
       </c>
     </row>
@@ -2906,29 +2906,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43c280e0db347ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4a885f309c1d91</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Swift Developer</t>
+          <t>Senior Analytics Engineer - On-Site (Texas)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Southside Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4a885f309c1d91</t>
+          <t>https://www.indeed.com/viewjob?jk=c35333a91d42cd16</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
+          <t>https://www.indeed.com/viewjob?jk=8f01cd759e7e2639</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
+          <t>https://www.indeed.com/viewjob?jk=b8b790018e6435ce</t>
         </is>
       </c>
     </row>
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
+          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - On-Site (Texas)</t>
+          <t>Senior Java Backend Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Southside Bank</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c35333a91d42cd16</t>
+          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Trulioo</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f01cd759e7e2639</t>
+          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ba83b80a06bd79</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3264f58d94550</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Associate AI Software Engineer</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Asure Software</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,42 +3286,42 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, DynamoDB, NoSQL, ETL, CI/CD, Git, Python</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad7eaf60ccf42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b18a3410ca26c21c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Senior Full Stack Engineer, Client Platform</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18a3410ca26c21c</t>
+          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Client Platform</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
+          <t>AWS, IAM, Scala, ELT, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce11b9433c91a10</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, ELT, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce11b9433c91a10</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4b33ddd29938b6</t>
         </is>
       </c>
     </row>
@@ -3443,12 +3443,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Oracle Fusion Senior Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70d46bede5c9eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Oracle Fusion Architect</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>Ketch</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa8a2e6fc3e9671</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ketch</t>
+          <t>Eko Green Industrial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
+          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Application Developer III 4P/797</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>S3, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0a2d794a3a9143</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Eko Green Industrial</t>
+          <t>DANTA TECHNOLOGIES PVT LTD</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba4909bc0770b1b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer III 4P/797</t>
+          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3680,41 +3680,6 @@
         </is>
       </c>
       <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0a2d794a3a9143</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
         </is>

--- a/results/job_matches_2026-08-06.xlsx
+++ b/results/job_matches_2026-08-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (contract)</t>
+          <t>Azure ETL Architect – Data Modernization</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Medallion Architecture, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9e7e1df6ea458d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb3d2789d2f0f62</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce580424ef8e2efe</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9e7e1df6ea458d</t>
         </is>
       </c>
     </row>
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ee6d54792e5b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce580424ef8e2efe</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Senior Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=644b32ef05018543</t>
+          <t>https://www.indeed.com/viewjob?jk=96ee6d54792e5b0e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer(Python)</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e81248d8fcac15</t>
+          <t>https://www.indeed.com/viewjob?jk=644b32ef05018543</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer(Python)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3b83404ecad769</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e81248d8fcac15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Java Engineer - Kafka &amp; AWS MSK Migration - Client Site</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13319eb3c1502937</t>
+          <t>https://www.indeed.com/viewjob?jk=be3b83404ecad769</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Java Engineer - Kafka &amp; AWS MSK Migration - Client Site</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BSF</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc8f770215e2b11</t>
+          <t>https://www.indeed.com/viewjob?jk=13319eb3c1502937</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>BSF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7accc6e59fc97f98</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc8f770215e2b11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12298937e96ea8b</t>
+          <t>https://www.indeed.com/viewjob?jk=7accc6e59fc97f98</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Warehousing Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, ECS, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f0db046b81c4b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=a12298937e96ea8b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Warehousing Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, ECS, RDS, Databricks</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4680bf14d32cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=1f0db046b81c4b7e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Java with Angular - Onsite - Atlanta/Alpharetta</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c752e537cd0c2e4</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4680bf14d32cc9</t>
         </is>
       </c>
     </row>
@@ -981,29 +981,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476324ac0bfc1988</t>
+          <t>https://www.indeed.com/viewjob?jk=2c752e537cd0c2e4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Senior Architect</t>
+          <t>Full Stack Java with Angular - Onsite - Atlanta/Alpharetta</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d8b3a17d5ca1b6</t>
+          <t>https://www.indeed.com/viewjob?jk=476324ac0bfc1988</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Cloud &amp; Data Senior Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
+          <t>https://www.indeed.com/viewjob?jk=56d8b3a17d5ca1b6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bally's Intralot</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4a5cb09b0891fe</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GovCloud/FedRAMP)</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>Bally's Intralot</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b64846e4342be04</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4a5cb09b0891fe</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Digital Customer Experience</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fa71cd2f8a99fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c2dc5b2bfc7d7bdc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>AI Security Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2dc5b2bfc7d7bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Security Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mizuho Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
+          <t>https://www.indeed.com/viewjob?jk=e4572b56a2bddf9a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer IV. 4P/796</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mizuho Bank</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4572b56a2bddf9a</t>
+          <t>https://www.indeed.com/viewjob?jk=52cb4b188a57c118</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer IV. 4P/796</t>
+          <t>MO 85- Power BI and Data engineer (806590)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Fellowship Health Resources, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52cb4b188a57c118</t>
+          <t>https://www.indeed.com/viewjob?jk=5000cd2f1efb32c2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MO 85- Power BI and Data engineer (806590)</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fellowship Health Resources, Inc.</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5000cd2f1efb32c2</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdabe0fd11a2b20</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>ITgen systems</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Andes, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdabe0fd11a2b20</t>
+          <t>https://www.indeed.com/viewjob?jk=3558a4604fdf437b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ITgen systems</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Andes, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3558a4604fdf437b</t>
+          <t>https://www.indeed.com/viewjob?jk=978c47b533d24327</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Contact Center Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=978c47b533d24327</t>
+          <t>https://www.indeed.com/viewjob?jk=fafd113ac8d024d0</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafd113ac8d024d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f947249f6b00842e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f947249f6b00842e</t>
+          <t>https://www.indeed.com/viewjob?jk=284f70ca41d0b336</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=284f70ca41d0b336</t>
+          <t>https://www.indeed.com/viewjob?jk=ee98575464cd3291</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee98575464cd3291</t>
+          <t>https://www.indeed.com/viewjob?jk=063baf5a6448568c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Engineer I, Burger King</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Burger King</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=063baf5a6448568c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea7e1f2c36a21591</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea7e1f2c36a21591</t>
+          <t>https://www.indeed.com/viewjob?jk=eef1687719f12bcd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Power BI Developer – Data Modernization</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef1687719f12bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=b721420913a99a6c</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>EDS Front End Architect (Remote)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064915e533631ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=4355de47b9364410</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EDS Front End Architect (Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4355de47b9364410</t>
+          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Integration Engineer, Business Systems</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Scala, Snowflake, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
+          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer, Business Systems</t>
+          <t>Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Johnston, IA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Scala, Snowflake, Oracle, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Databricks Lakehouse, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
+          <t>https://www.indeed.com/viewjob?jk=03849a706ec32867</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Databricks</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IMG</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Johnston, IA, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Databricks Lakehouse, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03849a706ec32867</t>
+          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
         </is>
       </c>
     </row>
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Swift Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4a885f309c1d91</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Swift Developer</t>
+          <t>Senior Analytics Engineer - On-Site (Texas)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Southside Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4a885f309c1d91</t>
+          <t>https://www.indeed.com/viewjob?jk=c35333a91d42cd16</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - On-Site (Texas)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Southside Bank</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c35333a91d42cd16</t>
+          <t>https://www.indeed.com/viewjob?jk=b8b790018e6435ce</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,24 +3006,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8b790018e6435ce</t>
+          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Senior Java Backend Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Hybrid)</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
+          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior IT Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NYC EMPLOYEES RETIREMENT SYS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NYC EMPLOYEES RETIREMENT SYS</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3264f58d94550</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Escalon</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,94 +3226,94 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c92bfd88d73cefea</t>
+          <t>https://www.indeed.com/viewjob?jk=b18a3410ca26c21c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, IAM, Scala, ELT, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3264f58d94550</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce11b9433c91a10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18a3410ca26c21c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4b33ddd29938b6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Client Platform</t>
+          <t>Gen AI Solutions Engineer #122</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Premier Cloud</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SQS, SNS, ECS, RDS, Kafka, PostgreSQL, MySQL, CI/CD, Kubernetes, pytest</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6579a2f1e0419a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=ead4e34bd1038d2d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, ELT, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce11b9433c91a10</t>
+          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Ketch</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4b33ddd29938b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Gen AI Solutions Engineer #122</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Premier Cloud</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead4e34bd1038d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Application Developer III 4P/797</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
+          <t>S3, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0a2d794a3a9143</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ketch</t>
+          <t>DANTA TECHNOLOGIES PVT LTD</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba4909bc0770b1b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3540,146 +3540,6 @@
         </is>
       </c>
       <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Software Engineer (Remote) - Sustainable Tech Solutions</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Eko Green Industrial</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Miami Lakes, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2025-02-03</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4443bc0700cde0e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Full Stack Application Developer III 4P/797</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>4P Consulting Inc.</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0a2d794a3a9143</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Azure Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>DANTA TECHNOLOGIES PVT LTD</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba4909bc0770b1b</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
         </is>

--- a/results/job_matches_2026-08-06.xlsx
+++ b/results/job_matches_2026-08-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior AI / Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Celebration, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Oozie, YARN, Impala</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e283799e17891679</t>
+          <t>https://www.indeed.com/viewjob?jk=4a1d158814d4803d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Azure ETL Architect – Data Modernization</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Medallion Architecture, Dataflow, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Oozie, YARN, Impala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb3d2789d2f0f62</t>
+          <t>https://www.indeed.com/viewjob?jk=e283799e17891679</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (contract)</t>
+          <t>Azure ETL Architect – Data Modernization</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Medallion Architecture, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9e7e1df6ea458d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb3d2789d2f0f62</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce580424ef8e2efe</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9e7e1df6ea458d</t>
         </is>
       </c>
     </row>
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ee6d54792e5b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce580424ef8e2efe</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Senior Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=644b32ef05018543</t>
+          <t>https://www.indeed.com/viewjob?jk=96ee6d54792e5b0e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer(Python)</t>
+          <t>Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e81248d8fcac15</t>
+          <t>https://www.indeed.com/viewjob?jk=644b32ef05018543</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer(Python)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3b83404ecad769</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e81248d8fcac15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Java Engineer - Kafka &amp; AWS MSK Migration - Client Site</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13319eb3c1502937</t>
+          <t>https://www.indeed.com/viewjob?jk=be3b83404ecad769</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Java Engineer - Kafka &amp; AWS MSK Migration - Client Site</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BSF</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc8f770215e2b11</t>
+          <t>https://www.indeed.com/viewjob?jk=13319eb3c1502937</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack Java with Angular - Onsite - Atlanta/Alpharetta</t>
+          <t>Cloud &amp; Data Senior Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476324ac0bfc1988</t>
+          <t>https://www.indeed.com/viewjob?jk=56d8b3a17d5ca1b6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Senior Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>AmeriLife</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,42 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d8b3a17d5ca1b6</t>
+          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Aivanta Tech Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Michigan, ND, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
+          <t>https://www.indeed.com/viewjob?jk=403ce6d0a4bc7ec2</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, API Gateway, ECS, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699af075d40be5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=d45dda7076140234</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2dc5b2bfc7d7bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=699af075d40be5fc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Security Architect</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, NoSQL, MLOps, MLflow</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
+          <t>https://www.indeed.com/viewjob?jk=c2dc5b2bfc7d7bdc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Security Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mizuho Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4572b56a2bddf9a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer IV. 4P/796</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Mizuho Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52cb4b188a57c118</t>
+          <t>https://www.indeed.com/viewjob?jk=e4572b56a2bddf9a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MO 85- Power BI and Data engineer (806590)</t>
+          <t>Data Analytics Engineer IV. 4P/796</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fellowship Health Resources, Inc.</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5000cd2f1efb32c2</t>
+          <t>https://www.indeed.com/viewjob?jk=52cb4b188a57c118</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>MO 85- Power BI and Data engineer (806590)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Fellowship Health Resources, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdabe0fd11a2b20</t>
+          <t>https://www.indeed.com/viewjob?jk=5000cd2f1efb32c2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ITgen systems</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Andes, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3558a4604fdf437b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdabe0fd11a2b20</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MySQL, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665101d138f0765c</t>
+          <t>https://www.indeed.com/viewjob?jk=d01db6639e88fcab</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Full-Stack Platform Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01db6639e88fcab</t>
+          <t>https://www.indeed.com/viewjob?jk=4b64ece3d83e461e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full-Stack Platform Software Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b64ece3d83e461e</t>
+          <t>https://www.indeed.com/viewjob?jk=766c2d4ea3852d27</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766c2d4ea3852d27</t>
+          <t>https://www.indeed.com/viewjob?jk=2378c1e094af5b61</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Mid-Level Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2378c1e094af5b61</t>
+          <t>https://www.indeed.com/viewjob?jk=8e904477144f9b0f</t>
         </is>
       </c>
     </row>
@@ -1973,25 +1973,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mid-Level Software Engineer</t>
+          <t>Data Engineer (GCP, BigQuery)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>Redshift, Azure, Synapse Analytics, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e904477144f9b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=d730d92415b574ca</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, BigQuery)</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Synapse Analytics, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Databricks Lakehouse</t>
+          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d730d92415b574ca</t>
+          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Flexjet, LLC.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8864424fa1770f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Engineer III - Platform Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8864424fa1770f</t>
+          <t>https://www.indeed.com/viewjob?jk=93749d43fe3ef5d1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer III - Platform Data Engineer (Remote)</t>
+          <t>Senior Engineer, Data Management</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93749d43fe3ef5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Management</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Rivo Holdings</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, Fact Tables</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
+          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rivo Holdings</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, Fact Tables</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
+          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
+          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Java Full Stack Software Engineer III - React / PostgreSQL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
+          <t>https://www.indeed.com/viewjob?jk=5098c1122253111e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java Full Stack Software Engineer III - React / PostgreSQL</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Maitland, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk</t>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5098c1122253111e</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
+          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Database Administrator IV</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=224c101cb5cb9b32</t>
         </is>
       </c>
     </row>
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224c101cb5cb9b32</t>
+          <t>https://www.indeed.com/viewjob?jk=4752fa061c12fdd3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Database Administrator IV</t>
+          <t>Senior Analyst, Project Support - Strategic Operations</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4752fa061c12fdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=5e873d0306e737e8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>Data Engineer 3 - Virtual</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e873d0306e737e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e58245a6fd122ca7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Virtual</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Radix</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58245a6fd122ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=436f3c432785fc82</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect/Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Radix</t>
+          <t>AAR Corp.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Wood Dale, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,19 +2561,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436f3c432785fc82</t>
+          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Cloud/Site Reliability Engineer</t>
+          <t>EDS Front End Architect (Remote)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c967cc75affe93</t>
+          <t>https://www.indeed.com/viewjob?jk=4355de47b9364410</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Solution Architect/Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AAR Corp.</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wood Dale, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
+          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EDS Front End Architect (Remote)</t>
+          <t>Senior Integration Engineer, Business Systems</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Scala, Snowflake, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4355de47b9364410</t>
+          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>IMG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Johnston, IA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Databricks Lakehouse, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
+          <t>https://www.indeed.com/viewjob?jk=03849a706ec32867</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer, Business Systems</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Scala, Snowflake, Oracle, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
+          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Databricks</t>
+          <t>Associate Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IMG</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Johnston, IA, US USA</t>
+          <t>Blacksburg, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Databricks Lakehouse, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03849a706ec32867</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Senior Analytics Engineer - On-Site (Texas)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Southside Bank</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c35333a91d42cd16</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Data and Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Blacksburg, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
+          <t>https://www.indeed.com/viewjob?jk=b8b790018e6435ce</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Swift Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Trulioo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4a885f309c1d91</t>
+          <t>https://www.indeed.com/viewjob?jk=8f01cd759e7e2639</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - On-Site (Texas)</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Southside Bank</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c35333a91d42cd16</t>
+          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Backend Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8b790018e6435ce</t>
+          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Java Backend Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Trulioo</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f01cd759e7e2639</t>
+          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Hybrid)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3264f58d94550</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b18a3410ca26c21c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Scala, ELT, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce11b9433c91a10</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior IT Architect</t>
+          <t>Senior Solutions Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NYC EMPLOYEES RETIREMENT SYS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3142,108 +3142,108 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a29445aa2fe8226</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer - Integrations - AI/ML</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Spark, Kafka, Kafka Connect, Data Modeling, dbt, Tableau, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3264f58d94550</t>
+          <t>https://www.indeed.com/viewjob?jk=828c2593dd3b6144</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18a3410ca26c21c</t>
+          <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, ELT, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce11b9433c91a10</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4b33ddd29938b6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Gen AI Solutions Engineer #122</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Premier Cloud</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4b33ddd29938b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ead4e34bd1038d2d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Gen AI Solutions Engineer #122</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Premier Cloud</t>
+          <t>AssistRx</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ead4e34bd1038d2d</t>
+          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AssistRx</t>
+          <t>Ketch</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ketch</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Application Developer III 4P/797</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>S3, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0a2d794a3a9143</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer III 4P/797</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>DANTA TECHNOLOGIES PVT LTD</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,77 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0a2d794a3a9143</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Azure Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>DANTA TECHNOLOGIES PVT LTD</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=9ba4909bc0770b1b</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Virtualization and SIL Integration</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11cf4bcf3a74bb14</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-06.xlsx
+++ b/results/job_matches_2026-08-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,35 +503,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Oozie, YARN, Impala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e283799e17891679</t>
+          <t>https://www.indeed.com/viewjob?jk=93b179b1cd108b7b</t>
         </is>
       </c>
     </row>
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (contract)</t>
+          <t>Junior Data Engineer (GCP Cloud Migrations)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,252 +591,252 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9e7e1df6ea458d</t>
+          <t>https://www.indeed.com/viewjob?jk=221a082ea5ba73e5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (contract)</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>SambaSafety</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, SQS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce580424ef8e2efe</t>
+          <t>https://www.indeed.com/viewjob?jk=e36968d9c7ac52ee</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (contract)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Cloud Storage, Hadoop, HDFS, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96ee6d54792e5b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbe4c00163046c9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Senior Data Engineer (Microsoft Fabric / Financial Data)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=644b32ef05018543</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a05cc1e1075c25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer(Python)</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e81248d8fcac15</t>
+          <t>https://www.indeed.com/viewjob?jk=785c8caf68e944db</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>American Eagle Outfitters</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Databricks, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3b83404ecad769</t>
+          <t>https://www.indeed.com/viewjob?jk=7f044661c236d0fa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Java Engineer - Kafka &amp; AWS MSK Migration - Client Site</t>
+          <t>Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Aivanta Tech Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Michigan, ND, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Kafka, Kafka Connect, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13319eb3c1502937</t>
+          <t>https://www.indeed.com/viewjob?jk=403ce6d0a4bc7ec2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>Bally's Intralot</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7accc6e59fc97f98</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4a5cb09b0891fe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, ECS, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12298937e96ea8b</t>
+          <t>https://www.indeed.com/viewjob?jk=d45dda7076140234</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Warehousing Specialist</t>
+          <t>Database Engineer - onsite</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Eccalon</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, ECS, RDS, Databricks</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f0db046b81c4b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=c2dc5b2bfc7d7bdc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Alliance Laundry</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4680bf14d32cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=c04148de4bd6f9b0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Java with Angular - Onsite - Atlanta/Alpharetta</t>
+          <t>Data Analytics Engineer IV. 4P/796</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,116 +972,116 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c752e537cd0c2e4</t>
+          <t>https://www.indeed.com/viewjob?jk=52cb4b188a57c118</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud &amp; Data Senior Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, MySQL, Fact Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d8b3a17d5ca1b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3993278550c57650</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AmeriLife</t>
+          <t>Synectics for Management Decisions Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7b39b4bbadec2a</t>
+          <t>https://www.indeed.com/viewjob?jk=878ba8f484655f37</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud &amp; DevOps Engineer</t>
+          <t>Sr Software Engineer - Full stack</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aivanta Tech Inc</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Michigan, ND, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403ce6d0a4bc7ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=132ff9cd67bd84f1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bally's Intralot</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4a5cb09b0891fe</t>
+          <t>https://www.indeed.com/viewjob?jk=d147aecd8090091a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,137 +1161,137 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45dda7076140234</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff7f502ba85d5a1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
+          <t>Sr Data Engineer Consultant - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=699af075d40be5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4b101e186a751f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Database Engineer - onsite</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Eccalon</t>
+          <t>American Public Education, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2dc5b2bfc7d7bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=7583012c770de15f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Security Architect</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2895861185e447</t>
+          <t>https://www.indeed.com/viewjob?jk=eef1687719f12bcd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Developer – Data Modernization</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mizuho Bank</t>
+          <t>Cyberlocke, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,172 +1301,172 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4572b56a2bddf9a</t>
+          <t>https://www.indeed.com/viewjob?jk=b721420913a99a6c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer IV. 4P/796</t>
+          <t>Python Integration Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>K12 Plus Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Angelo, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, RDS, Azure, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52cb4b188a57c118</t>
+          <t>https://www.indeed.com/viewjob?jk=8096314641677e89</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MO 85- Power BI and Data engineer (806590)</t>
+          <t>CDP System Developer (Customer Data Platform)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fellowship Health Resources, Inc.</t>
+          <t>Avantor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5000cd2f1efb32c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea80ec9d97ad1a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>AI/ML ENG III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Fujitsu</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdabe0fd11a2b20</t>
+          <t>https://www.indeed.com/viewjob?jk=c79fecb88f759cdc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Oracle, Snowflake Schema, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=978c47b533d24327</t>
+          <t>https://www.indeed.com/viewjob?jk=500dd12f156b94bf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Engineer (GCP, BigQuery)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>Redshift, Azure, Synapse Analytics, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,102 +1476,102 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafd113ac8d024d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d730d92415b574ca</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Engineer III - Platform Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f947249f6b00842e</t>
+          <t>https://www.indeed.com/viewjob?jk=93749d43fe3ef5d1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Atrium Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=284f70ca41d0b336</t>
+          <t>https://www.indeed.com/viewjob?jk=eec27aaa2f43f1a1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Database Administrator IV</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee98575464cd3291</t>
+          <t>https://www.indeed.com/viewjob?jk=224c101cb5cb9b32</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Database Administrator IV</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=063baf5a6448568c</t>
+          <t>https://www.indeed.com/viewjob?jk=4752fa061c12fdd3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer I, Burger King</t>
+          <t>Data Engineer 3 - Virtual</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Burger King</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea7e1f2c36a21591</t>
+          <t>https://www.indeed.com/viewjob?jk=e58245a6fd122ca7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>American Public Education, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,277 +1686,277 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef1687719f12bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=68ab47cb79e889c6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Power BI Developer – Data Modernization</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cyberlocke, LLC</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b721420913a99a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=91d2862f61030bf6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior ML Engineer (Data Scientist)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Data Modeling, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5f74b5ca1d0e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=a680bbd22cb24e19</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Woodland Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Power BI, Tableau, MLOps, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01db6639e88fcab</t>
+          <t>https://www.indeed.com/viewjob?jk=ad9b7febafc66a63</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full-Stack Platform Software Engineer</t>
+          <t>Full Stack Engineer I</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, PostgreSQL, MySQL, NoSQL</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, SQL Server, Azure Cosmos DB, NoSQL, REST API integration, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b64ece3d83e461e</t>
+          <t>https://www.indeed.com/viewjob?jk=d50322779edaaaaf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Cavnue</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Cloud Storage, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766c2d4ea3852d27</t>
+          <t>https://www.indeed.com/viewjob?jk=02ebda82ef06209d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Specialist, AI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Entegris</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Bedford, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2378c1e094af5b61</t>
+          <t>https://www.indeed.com/viewjob?jk=26996de4972347a2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mid-Level Software Engineer</t>
+          <t>Data Acquisition Engineer I</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AAA Washington</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, PySpark, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e904477144f9b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=19e940607fea1d4f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI/ML ENG III</t>
+          <t>Sr Product Owner</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fujitsu</t>
+          <t>Jack Link's Protein Snacks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c79fecb88f759cdc</t>
+          <t>https://www.indeed.com/viewjob?jk=4eba90eff680f3f7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, BigQuery)</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Synapse Analytics, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, SQL Server, MongoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d730d92415b574ca</t>
+          <t>https://www.indeed.com/viewjob?jk=683b7ea806b3acd7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Analytics Engineer - On-Site (Texas)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Southside Bank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Oozie, Spark, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca295e881951a0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=c35333a91d42cd16</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Flexjet, LLC.</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8864424fa1770f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92f9489f241300</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Engineer III - Platform Data Engineer (Remote)</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Data Modeling, dbt, CI/CD, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93749d43fe3ef5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2a88e891b2b83b32</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Management</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485768e2c5e94d4b</t>
+          <t>https://www.indeed.com/viewjob?jk=baf189385744be39</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rivo Holdings</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Scala, Snowflake, Dimensional Modeling, Star Schema, Snowflake Schema, Fact Tables</t>
+          <t>AWS, IAM, Scala, ELT, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,277 +2176,277 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30d873fbb78ff247</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce11b9433c91a10</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a04dc5f4119a86a</t>
+          <t>https://www.indeed.com/viewjob?jk=2995ab20e728a84b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, CI/CD, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e58256f001ecd6</t>
+          <t>https://www.indeed.com/viewjob?jk=33b6b6de106ec251</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java Full Stack Software Engineer III - React / PostgreSQL</t>
+          <t>Full-Stack Software Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>IceKredit</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, MySQL, MLOps, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5098c1122253111e</t>
+          <t>https://www.indeed.com/viewjob?jk=9738c4960b56ad75</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data &amp; BI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Maitland, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Snowflake, PostgreSQL, ETL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, MongoDB, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a42c056eadbcf3</t>
+          <t>https://www.indeed.com/viewjob?jk=06504bc008d0919a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Solutions Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c86fe9a869ba3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Database Administrator IV</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224c101cb5cb9b32</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4b33ddd29938b6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Database Administrator IV</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Ketch</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4752fa061c12fdd3</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Analyst, Project Support - Strategic Operations</t>
+          <t>Full Stack Application Developer III 4P/797</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Scala, Snowflake, SQL Server, MySQL, Snowflake Schema, ETL, Power BI, MicroStrategy</t>
+          <t>S3, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,1022 +2456,77 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e873d0306e737e8</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0a2d794a3a9143</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - Virtual</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Monogram Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58245a6fd122ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Integrations - AI/ML</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Radix</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Spark, Kafka, Kafka Connect, Data Modeling, dbt, Tableau, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436f3c432785fc82</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Solution Architect/Data Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>AAR Corp.</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Wood Dale, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2254089b8b9a66f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>EDS Front End Architect (Remote)</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Blue Acorn iCi</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Spark, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4355de47b9364410</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>DocuSign</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10af69983fe65f09</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Integration Engineer, Business Systems</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Databricks, Scala, Snowflake, Oracle, CI/CD</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b31fe03b3202aa0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Azure Data Engineer with Databricks</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>IMG</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Johnston, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, Databricks Lakehouse, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03849a706ec32867</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Associate Data and Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Virginia Tech</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Blacksburg, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4801f1e85e3ac4b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Associate Data and Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Virginia Tech</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Blacksburg, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau, MicroStrategy</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7c91c3c9b4df97</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer - On-Site (Texas)</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Southside Bank</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Tyler, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c35333a91d42cd16</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8b790018e6435ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Trulioo</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f01cd759e7e2639</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Senior Java Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eebe0f08857d67b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Senior Java Backend Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7627196fd1190db1</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Java Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7bce0ed4f22212c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Santa Monica, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7482535c924ec6a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3264f58d94550</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b18a3410ca26c21c</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>CLERA</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Scala, ELT, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce11b9433c91a10</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f7f816ce641e12</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Integrations - AI/ML</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>clickhouse</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, Kafka, Kafka Connect, Data Modeling, dbt, Tableau, MLOps, Airflow</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=828c2593dd3b6144</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Monogram Health</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, MLflow, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fe0dee1e8474ed0</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Allen Park, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4b33ddd29938b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Gen AI Solutions Engineer #122</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Premier Cloud</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ead4e34bd1038d2d</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>AssistRx</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, ETL</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29e2a93d07b12647</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Backend Software Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Ketch</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, DynamoDB, Cassandra, Data Modeling, CI/CD, GitHub Actions, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5d2c1be2dfe526</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Ascendion</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9a638f7797a3de</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Full Stack Application Developer III 4P/797</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>4P Consulting Inc.</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0a2d794a3a9143</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Azure Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>DANTA TECHNOLOGIES PVT LTD</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba4909bc0770b1b</t>
         </is>
       </c>
     </row>
